--- a/etf_holdings/2026-08-26_common_holdings_all.xlsx
+++ b/etf_holdings/2026-08-26_common_holdings_all.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.09%</t>
+          <t>9.90%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -602,11 +602,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>12.71%</t>
+          <t>11.80%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4500000</v>
+        <v>4200000</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>8.67%</t>
+          <t>8.50%</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -641,7 +641,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>17.14%</t>
+          <t>16.87%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -667,7 +667,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>7.40%</t>
+          <t>7.24%</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -688,12 +688,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>81.63%</t>
+          <t>79.93%</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>10.20%</t>
+          <t>9.99%</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.59%</t>
+          <t>9.85%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -736,7 +736,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9.22%</t>
+          <t>9.60%</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3.63%</t>
+          <t>3.72%</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -775,7 +775,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>5.63%</t>
+          <t>5.80%</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>6.14%</t>
+          <t>6.29%</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -822,12 +822,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>42.96%</t>
+          <t>44.01%</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>5.37%</t>
+          <t>5.50%</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6.80%</t>
+          <t>7.01%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -870,7 +870,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.39%</t>
+          <t>4.59%</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>6.56%</t>
+          <t>6.75%</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -909,7 +909,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>4.69%</t>
+          <t>4.85%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.41%</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>32.78%</t>
+          <t>33.60%</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>4.10%</t>
+          <t>4.20%</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.71%</t>
+          <t>4.65%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1004,11 +1004,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.18%</t>
+          <t>4.07%</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1750000</v>
+        <v>1700000</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.93%</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.76%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>5.15%</t>
+          <t>5.06%</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>25.03%</t>
+          <t>24.70%</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.95%</t>
+          <t>3.92%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.44%</t>
+          <t>4.46%</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="R6" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13.71%</t>
+          <t>13.68%</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4.07%</t>
+          <t>3.98%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.76%</t>
         </is>
       </c>
       <c r="R7" t="n">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13.58%</t>
+          <t>13.38%</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
